--- a/template/template_kehadiran.xlsx
+++ b/template/template_kehadiran.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\rekap_v2\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6043E01E-3D50-4135-AE3C-3C1F3C733007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DEB5F1-27B6-47D3-B9C2-28133D41CEC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A249A33A-857A-48A1-8966-38D764EF4AFF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>NO</t>
   </si>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t>SAKIT</t>
+  </si>
+  <si>
+    <t>LAST_UPDATE</t>
+  </si>
+  <si>
+    <t>13 *(2024/01/31)</t>
   </si>
 </sst>
 </file>
@@ -451,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16A7B10B-DA90-4064-B7BC-91FADC2F53D1}">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.6640625" bestFit="1" customWidth="1"/>
@@ -468,7 +474,7 @@
     <col min="13" max="13" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -508,8 +514,11 @@
       <c r="M1" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="N1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -548,6 +557,9 @@
       </c>
       <c r="M2" s="1">
         <v>12</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
